--- a/Extractor de datos/registros/check_in_maestro.xlsx
+++ b/Extractor de datos/registros/check_in_maestro.xlsx
@@ -1,103 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisl\Documents\SOLH\Extractor de datos\registros\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8041DC15-AAA5-405C-919B-284403F5F39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>nombre</t>
-  </si>
-  <si>
-    <t>apellido_paterno</t>
-  </si>
-  <si>
-    <t>apellido_materno</t>
-  </si>
-  <si>
-    <t>curp</t>
-  </si>
-  <si>
-    <t>fecha_nacimiento</t>
-  </si>
-  <si>
-    <t>sexo</t>
-  </si>
-  <si>
-    <t>edad_calculada</t>
-  </si>
-  <si>
-    <t>es_mayor_de_edad</t>
-  </si>
-  <si>
-    <t>curp_valida</t>
-  </si>
-  <si>
-    <t>fecha_registro</t>
-  </si>
-  <si>
-    <t>archivo_fuente</t>
-  </si>
-  <si>
-    <t>EFRAIN</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MXME650303HTLRRF06</t>
-  </si>
-  <si>
-    <t>03/03/1965</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>2026-04-17 23:56:04</t>
-  </si>
-  <si>
-    <t>img1.jpg</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -116,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -418,83 +408,652 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="37.7109375" customWidth="1"/>
-    <col min="10" max="10" width="41" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>apellido_paterno</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>apellido_materno</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>curp</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fecha_nacimiento</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sexo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>edad_calculada</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>es_mayor_de_edad</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>curp_valida</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>fecha_registro</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>archivo_fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EFRAIN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MXME650303HTLRRF06</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>03/03/1965</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>61</v>
       </c>
-      <c r="H2" t="s">
-        <v>17</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
       </c>
       <c r="I2" t="b">
         <v>1</v>
       </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-04-17 23:56:04</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>img1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>JUANA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ALVA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BARRIOS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LULE230706MSLLYS04993</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>28/10/1940</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>85</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:03:09</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ine_test_0.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CORNELIO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CENTENO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VELA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HOAW160404MPLMCQA95</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1988-11-26</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:03:09</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ine_test_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DEBORA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OROSCO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>XEKQ670829HSPWBS08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15/08/1967</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>58</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:03:09</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ine_test_2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>QUINTANILLA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>UOFI130709HCLMDP00018</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>08/11/1934</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>91</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:03:09</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ine_test_3.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ZOÉ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PEDROZA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ROLDÁN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HEOH071210HASFFT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27/05/1993</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>32</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:03:09</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ine_test_4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SOCORRO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SEVILLA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SALAS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IUKX270310MSLNVY02006</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>29/08/1985</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:03:09</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ine_test_5.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ISRAEL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CASTELLANOS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>WOTC230513MTLGMMR04</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>18/03/1921</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>105</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:03:09</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ine_test_6.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LUCERO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VILLARREAL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CRISTIAN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>YAIX751117MOCLCI032008</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20/04/1992</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>33</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:03:09</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ine_test_7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RUFINO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ORTEGA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MENÉNDEZ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>WILJ421120HJCKZT092004</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>06/08/1992</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>33</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:03:09</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ine_test_8.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IRENE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ORTEGA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CORTÉS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OIFK830328MQRHYV01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>25/05/1953</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>72</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:03:09</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ine_test_9.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>
